--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_34.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_34.xlsx
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Diagnosis</t>
+          <t>Coffee?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9101138288620991</v>
+        <v>1.296400681660159</v>
       </c>
       <c r="C2">
-        <v>-0.9256902071087929</v>
+        <v>1.631351233997447</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.0466053968273916</v>
+        <v>0.6837725881611891</v>
       </c>
       <c r="C3">
-        <v>0.06429608550914576</v>
+        <v>1.445469669229108</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.6892016639781482</v>
+        <v>-0.6505237769675336</v>
       </c>
       <c r="C4">
-        <v>-1.252437350538746</v>
+        <v>-1.584543537088801</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.805045187873205</v>
+        <v>-0.03189534151426927</v>
       </c>
       <c r="C5">
-        <v>2.321683902794923</v>
+        <v>0.4334266822281317</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.04473131342062475</v>
+        <v>-1.562909143869611</v>
       </c>
       <c r="C6">
-        <v>1.007473474422538</v>
+        <v>1.339261341933168</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-2.28036664825053</v>
+        <v>-0.7668111307652432</v>
       </c>
       <c r="C7">
-        <v>1.004440318639472</v>
+        <v>-1.223746880051049</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8667233548833687</v>
+        <v>0.2671793748359568</v>
       </c>
       <c r="C8">
-        <v>-0.5559682054763165</v>
+        <v>0.2084767118653312</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0607801607828802</v>
+        <v>0.2385239860803963</v>
       </c>
       <c r="C9">
-        <v>1.599313514984528</v>
+        <v>-1.025850095584975</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.8636726024176926</v>
+        <v>0.5533246683708963</v>
       </c>
       <c r="C10">
-        <v>-0.1235903331365261</v>
+        <v>1.154368320413184</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-2.683159588247192</v>
+        <v>1.616689988382735</v>
       </c>
       <c r="C11">
-        <v>1.102085017370528</v>
+        <v>1.809939254391433</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.3053975427706018</v>
+        <v>-0.3911579558899318</v>
       </c>
       <c r="C12">
-        <v>-0.3815048356864417</v>
+        <v>1.216539245324391</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.254558077631851</v>
+        <v>1.0863170665186</v>
       </c>
       <c r="C13">
-        <v>-0.06905864278130042</v>
+        <v>1.139088382750797</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.4680174011834515</v>
+        <v>0.8596046987568375</v>
       </c>
       <c r="C14">
-        <v>0.447560383581536</v>
+        <v>0.4821423573830473</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.752876487436005</v>
+        <v>0.6659013879573746</v>
       </c>
       <c r="C15">
-        <v>-1.295276016348313</v>
+        <v>0.3108093277888222</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.4866208963325051</v>
+        <v>1.105713862688612</v>
       </c>
       <c r="C16">
-        <v>0.5080391631939873</v>
+        <v>0.2769419312250319</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.195784531839611</v>
+        <v>2.491048180532514</v>
       </c>
       <c r="C17">
-        <v>-2.26690639989492</v>
+        <v>-0.2445956953755077</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.03815358853756058</v>
+        <v>-0.2914625363779365</v>
       </c>
       <c r="C18">
-        <v>0.8957527363212719</v>
+        <v>-0.9410470668030055</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.4066955986569309</v>
+        <v>-0.5450045257493552</v>
       </c>
       <c r="C19">
-        <v>-0.7028118742477172</v>
+        <v>-0.2724478557288159</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.2230494173158245</v>
+        <v>-1.869682811106851</v>
       </c>
       <c r="C20">
-        <v>0.1443441210920309</v>
+        <v>-1.195542293640759</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.4279938544412866</v>
+        <v>-1.734432847315616</v>
       </c>
       <c r="C21">
-        <v>1.035931389233312</v>
+        <v>-0.9687526512231841</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.6328688737940171</v>
+        <v>-1.277505793353938</v>
       </c>
       <c r="C22">
-        <v>1.016029830736234</v>
+        <v>-1.604045014680528</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.2315568693002472</v>
+        <v>-0.1232878670389605</v>
       </c>
       <c r="C23">
-        <v>-1.412012706045393</v>
+        <v>-0.462148188669957</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.4834868318594485</v>
+        <v>0.7794836138752879</v>
       </c>
       <c r="C24">
-        <v>0.4998995527364919</v>
+        <v>0.7362626430786697</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.234005005937156</v>
+        <v>0.03041055010752305</v>
       </c>
       <c r="C25">
-        <v>-0.9439971971085772</v>
+        <v>0.7314366804447244</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.2801361399427601</v>
+        <v>1.252507401411073</v>
       </c>
       <c r="C26">
-        <v>-0.8601415072970263</v>
+        <v>0.4765988955817089</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.6151452298004506</v>
+        <v>0.1245547302935808</v>
       </c>
       <c r="C27">
-        <v>0.550101897354403</v>
+        <v>-1.27575918952635</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.1502984243481142</v>
+        <v>-0.6234322425955152</v>
       </c>
       <c r="C28">
-        <v>0.247077643760807</v>
+        <v>-0.41979374100348</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.6336466638678031</v>
+        <v>0.07092419482858189</v>
       </c>
       <c r="C29">
-        <v>-0.245739030848506</v>
+        <v>-0.09497167155354838</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.6552138132612733</v>
+        <v>0.4028559341328806</v>
       </c>
       <c r="C30">
-        <v>0.7903783525736434</v>
+        <v>0.4353985297480876</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.345830461427634</v>
+        <v>-1.616674765349493</v>
       </c>
       <c r="C31">
-        <v>-2.473084626871795</v>
+        <v>0.00184603484543</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.355738991884192</v>
+        <v>0.2245905301331984</v>
       </c>
       <c r="C32">
-        <v>-0.08856078041200222</v>
+        <v>-0.01614020484461631</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.2929825780919288</v>
+        <v>0.4716844643437468</v>
       </c>
       <c r="C33">
-        <v>0.6662707566671759</v>
+        <v>-2.08411364098535</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4770753588221419</v>
+        <v>-1.85676963708648</v>
       </c>
       <c r="C34">
-        <v>0.2680684086912487</v>
+        <v>1.176439488083091</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.1642186463144801</v>
+        <v>0.8131067312300367</v>
       </c>
       <c r="C35">
-        <v>0.1160862255436245</v>
+        <v>0.4538912950084155</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.5765465208212183</v>
+        <v>0.6994065838355161</v>
       </c>
       <c r="C36">
-        <v>-0.3129062692489238</v>
+        <v>-0.5564604359516045</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.3885608158237651</v>
+        <v>-1.089110101885653</v>
       </c>
       <c r="C37">
-        <v>1.486843804953331</v>
+        <v>0.01746862946068184</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.7711506692358113</v>
+        <v>-0.3310569242534089</v>
       </c>
       <c r="C38">
-        <v>0.03681841399411534</v>
+        <v>1.793142044280714</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-2.048860645069468</v>
+        <v>-0.9111473941699917</v>
       </c>
       <c r="C39">
-        <v>0.2539837284415958</v>
+        <v>0.5535519773615745</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.83328115172117</v>
+        <v>0.08355966957401481</v>
       </c>
       <c r="C40">
-        <v>-0.179743300730397</v>
+        <v>-0.3779290240567161</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.9607048689204425</v>
+        <v>-1.359757595049211</v>
       </c>
       <c r="C41">
-        <v>0.2549407664327511</v>
+        <v>1.019433834678978</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.4284917653532215</v>
+        <v>0.1109600099096465</v>
       </c>
       <c r="C42">
-        <v>-0.7503697471470345</v>
+        <v>0.1885620080823209</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.3094782412597364</v>
+        <v>0.4637990102320871</v>
       </c>
       <c r="C43">
-        <v>1.174513345583788</v>
+        <v>-0.8237076923961151</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.30896393699328</v>
+        <v>0.3728107945790856</v>
       </c>
       <c r="C44">
-        <v>1.106202025141523</v>
+        <v>-1.024704594010654</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.07555839351238944</v>
+        <v>-0.7266441912525393</v>
       </c>
       <c r="C45">
-        <v>0.03769244726197498</v>
+        <v>-0.9030913027182819</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.256054502104698</v>
+        <v>-0.662923432656218</v>
       </c>
       <c r="C46">
-        <v>1.750905702460598</v>
+        <v>-1.144287315950613</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.023651285479921</v>
+        <v>1.600769246132006</v>
       </c>
       <c r="C47">
-        <v>0.5464981790226612</v>
+        <v>-0.7691449346698581</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.9107586910118749</v>
+        <v>0.7863871716444489</v>
       </c>
       <c r="C48">
-        <v>-2.032404795524463</v>
+        <v>0.4131926026478492</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.6465216186103795</v>
+        <v>1.106037308828145</v>
       </c>
       <c r="C49">
-        <v>-1.158757399705942</v>
+        <v>0.7700352501876228</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.068202304940014</v>
+        <v>0.4100989023799894</v>
       </c>
       <c r="C50">
-        <v>-0.1764794611978467</v>
+        <v>0.2888479157985299</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.302699025671308</v>
+        <v>0.1828559583121322</v>
       </c>
       <c r="C51">
-        <v>0.4264348704460111</v>
+        <v>-0.2037775093480213</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-1.064808206573379</v>
+        <v>0.004942618682272289</v>
       </c>
       <c r="C52">
-        <v>0.7229004380363011</v>
+        <v>0.5923743298725048</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.2734322967820448</v>
+        <v>-0.7298229091490411</v>
       </c>
       <c r="C53">
-        <v>-1.438105072289187</v>
+        <v>-0.6158692649205086</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.32951876066174</v>
+        <v>-0.141164903212003</v>
       </c>
       <c r="C54">
-        <v>-1.319887929178068</v>
+        <v>1.106035189779091</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.2050021135275434</v>
+        <v>-0.5294440344868449</v>
       </c>
       <c r="C55">
-        <v>0.1837772781962093</v>
+        <v>-0.6909275849276441</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.2226163582614764</v>
+        <v>0.2158026954657937</v>
       </c>
       <c r="C56">
-        <v>-0.7139953656467163</v>
+        <v>-1.241584602461228</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.07672907130441788</v>
+        <v>1.165413163033232</v>
       </c>
       <c r="C57">
-        <v>-0.00367321060417625</v>
+        <v>1.304709499973722</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>1.553464370533303</v>
+        <v>-0.864938803893225</v>
       </c>
       <c r="C58">
-        <v>-0.9845249157593519</v>
+        <v>-0.5053003516811331</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.6040629643417847</v>
+        <v>-0.6531529730410602</v>
       </c>
       <c r="C59">
-        <v>-0.5534656353711099</v>
+        <v>1.675749627868406</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.8541496314026574</v>
+        <v>0.1726311901598203</v>
       </c>
       <c r="C60">
-        <v>1.065600904119357</v>
+        <v>1.163331274391666</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-1.266110394618773</v>
+        <v>-0.08981201472438013</v>
       </c>
       <c r="C61">
-        <v>0.2754637923385979</v>
+        <v>1.244533122626488</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.1721373082193893</v>
+        <v>-1.538564445618051</v>
       </c>
       <c r="C62">
-        <v>-0.1991915016927645</v>
+        <v>-0.5957246465510878</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.9742830666109471</v>
+        <v>0.2389214044640204</v>
       </c>
       <c r="C63">
-        <v>-1.014009153123252</v>
+        <v>-0.6682320052171268</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.6161712939620048</v>
+        <v>0.9898423971453211</v>
       </c>
       <c r="C64">
-        <v>-0.7919751964770292</v>
+        <v>1.785530302864251</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.9164086834647285</v>
+        <v>0.399120400053366</v>
       </c>
       <c r="C65">
-        <v>-1.992463629149579</v>
+        <v>-0.03111858705215126</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.2083568023414195</v>
+        <v>-1.487064481131892</v>
       </c>
       <c r="C66">
-        <v>0.8899687676389227</v>
+        <v>-1.242548896681765</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.9065482358356853</v>
+        <v>0.0005543262861916508</v>
       </c>
       <c r="C67">
-        <v>-0.5377080118172399</v>
+        <v>-1.046489817506082</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-0.5154073749731866</v>
+        <v>1.004717075053885</v>
       </c>
       <c r="C68">
-        <v>0.5050662575700853</v>
+        <v>1.009546602474908</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.3152181862536826</v>
+        <v>-0.4231015584752262</v>
       </c>
       <c r="C69">
-        <v>0.01215548057144136</v>
+        <v>-0.07471655403025257</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.05904595972122029</v>
+        <v>0.400988869846494</v>
       </c>
       <c r="C70">
-        <v>2.439987258728677</v>
+        <v>0.4013075994214507</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.386833233358627</v>
+        <v>-0.4695981851953854</v>
       </c>
       <c r="C71">
-        <v>-0.09273447121513601</v>
+        <v>-0.5364882674045423</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.8174006322039155</v>
+        <v>1.783387625903336</v>
       </c>
       <c r="C72">
-        <v>-1.217056790137279</v>
+        <v>-0.2829472422823095</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>0.04061211188665489</v>
+        <v>-0.09393267408891039</v>
       </c>
       <c r="C73">
-        <v>-0.5891287060287549</v>
+        <v>-0.123307776696395</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.3874351807905922</v>
+        <v>-0.7003554979132486</v>
       </c>
       <c r="C74">
-        <v>0.8319398364600168</v>
+        <v>-1.049636301200922</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.01484664103676802</v>
+        <v>-0.5142368887026357</v>
       </c>
       <c r="C75">
-        <v>1.668781935317348</v>
+        <v>0.2199156960107575</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.1477622742444329</v>
+        <v>-0.961705559194593</v>
       </c>
       <c r="C76">
-        <v>-0.1151743990741279</v>
+        <v>0.16936731821697</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.2048215707709271</v>
+        <v>0.4053416274676786</v>
       </c>
       <c r="C77">
-        <v>0.7094719262779747</v>
+        <v>0.1802283583961765</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.3742929122150556</v>
+        <v>0.9375457102419107</v>
       </c>
       <c r="C78">
-        <v>0.6636458582230267</v>
+        <v>1.037566401181187</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.1284983140297655</v>
+        <v>0.4644729015920994</v>
       </c>
       <c r="C79">
-        <v>-0.574787246996447</v>
+        <v>-1.034973642291685</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>-0.640320048362861</v>
+        <v>3.223841305846292</v>
       </c>
       <c r="C80">
-        <v>0.09125985083313468</v>
+        <v>0.7001265520393071</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-0.4194610040396849</v>
+        <v>-0.5119565757976743</v>
       </c>
       <c r="C81">
-        <v>0.04511342565600013</v>
+        <v>0.4511489251386845</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.3767471688741192</v>
+        <v>0.9900191684564208</v>
       </c>
       <c r="C82">
-        <v>-0.6264882502842535</v>
+        <v>0.3796092814352046</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.497652928124235</v>
+        <v>-1.325816954548351</v>
       </c>
       <c r="C83">
-        <v>1.071601791584969</v>
+        <v>0.8366002869580407</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.1406531074627914</v>
+        <v>-0.5735965297304032</v>
       </c>
       <c r="C84">
-        <v>-0.3167835682395184</v>
+        <v>0.03021423768377568</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.9600454375597336</v>
+        <v>-0.440829910036774</v>
       </c>
       <c r="C85">
-        <v>-0.8003474855592877</v>
+        <v>0.8494373045440495</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.142169252653466</v>
+        <v>1.37781495585781</v>
       </c>
       <c r="C86">
-        <v>-0.7284967351479104</v>
+        <v>-0.2492925785968715</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.118698261794521</v>
+        <v>-0.2491412700586397</v>
       </c>
       <c r="C87">
-        <v>-1.020757936663906</v>
+        <v>0.1184118885491801</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.6572352441006249</v>
+        <v>-0.5443501832871092</v>
       </c>
       <c r="C88">
-        <v>1.420404933960413</v>
+        <v>0.2199106004674091</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.1087835628111845</v>
+        <v>-1.531808529515501</v>
       </c>
       <c r="C89">
-        <v>1.3893095333907</v>
+        <v>-1.031290452785834</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.3797942974441596</v>
+        <v>1.483709090872561</v>
       </c>
       <c r="C90">
-        <v>-1.028051739537671</v>
+        <v>1.574411309796765</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.1891318505060846</v>
+        <v>-0.3214615174327606</v>
       </c>
       <c r="C91">
-        <v>0.1582724565876155</v>
+        <v>-2.03525947703388</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.3188576917343221</v>
+        <v>0.05285903194532247</v>
       </c>
       <c r="C92">
-        <v>0.1412393637307398</v>
+        <v>-0.09166531783699206</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.5338323772890741</v>
+        <v>2.004453244722266</v>
       </c>
       <c r="C93">
-        <v>-0.01972716643987726</v>
+        <v>0.4393650525773565</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.7924874157535253</v>
+        <v>0.3363347358341396</v>
       </c>
       <c r="C94">
-        <v>0.9271581523977392</v>
+        <v>0.8278291209457799</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.9937951532607902</v>
+        <v>1.081780233801596</v>
       </c>
       <c r="C95">
-        <v>-0.09453310133723919</v>
+        <v>-0.111711392566158</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.1143355723095531</v>
+        <v>0.6735554329359131</v>
       </c>
       <c r="C96">
-        <v>-0.4241814299964019</v>
+        <v>-0.6450335515003689</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.3874115530575938</v>
+        <v>0.5128362798280593</v>
       </c>
       <c r="C97">
-        <v>0.4844154952051645</v>
+        <v>1.746813343725526</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.8796574824479473</v>
+        <v>0.3902208354450541</v>
       </c>
       <c r="C98">
-        <v>-0.07017076870593941</v>
+        <v>-0.3619841155466521</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.8099122123006545</v>
+        <v>0.364265048507345</v>
       </c>
       <c r="C99">
-        <v>0.02447878885643945</v>
+        <v>0.05478026338584481</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>-0.3391943090437392</v>
+        <v>-1.050918020886834</v>
       </c>
       <c r="C100">
-        <v>2.666858820008082</v>
+        <v>0.7646414949368898</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.6167261346033762</v>
+        <v>0.9968056189329721</v>
       </c>
       <c r="C101">
-        <v>0.5265302761386438</v>
+        <v>0.3352700471466339</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>-0.3451252445406303</v>
+        <v>1.093807529016803</v>
       </c>
       <c r="C102">
-        <v>1.467761736810244</v>
+        <v>0.1794414253071197</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.7652662060944426</v>
+        <v>-1.89426244908595</v>
       </c>
       <c r="C103">
-        <v>0.3227913482213532</v>
+        <v>-1.576308538033474</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>-0.3938404426484202</v>
+        <v>0.6359396301416723</v>
       </c>
       <c r="C104">
-        <v>-1.571868444502871</v>
+        <v>2.004097454581983</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.8449711958188698</v>
+        <v>-0.9289859247651219</v>
       </c>
       <c r="C105">
-        <v>0.7915536141036401</v>
+        <v>0.2153385164277442</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.1015769949214839</v>
+        <v>-0.07605242922799738</v>
       </c>
       <c r="C106">
-        <v>0.7599028601116373</v>
+        <v>-0.2288369418964337</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-0.2731267107857589</v>
+        <v>-0.6609677195998647</v>
       </c>
       <c r="C107">
-        <v>-2.151310493377503</v>
+        <v>1.183964761804827</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.529689228522466</v>
+        <v>0.9579009713571166</v>
       </c>
       <c r="C108">
-        <v>-0.7963988270407625</v>
+        <v>0.5468101851365306</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.1155360789498483</v>
+        <v>-0.2564421998281401</v>
       </c>
       <c r="C109">
-        <v>0.3255460073166063</v>
+        <v>-1.586235629789156</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.7739330484925523</v>
+        <v>-1.621954656976707</v>
       </c>
       <c r="C110">
-        <v>-0.8130796122191126</v>
+        <v>-0.04894419479323986</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.6047793585776688</v>
+        <v>0.6811780306340113</v>
       </c>
       <c r="C111">
-        <v>2.010659022998772</v>
+        <v>0.6273352670634647</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>-0.7631533572122642</v>
+        <v>-0.8850482994509232</v>
       </c>
       <c r="C112">
-        <v>-0.6204735620677312</v>
+        <v>-0.683415410575299</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-0.006385957776356426</v>
+        <v>0.5498931929595237</v>
       </c>
       <c r="C113">
-        <v>0.1342649766422434</v>
+        <v>0.545164493538447</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>-0.1607283679035795</v>
+        <v>-0.8697645650322958</v>
       </c>
       <c r="C114">
-        <v>1.965594892200768</v>
+        <v>-1.110378113791489</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.1888066817381341</v>
+        <v>0.03185771493870017</v>
       </c>
       <c r="C115">
-        <v>0.1395200571538298</v>
+        <v>-0.2483329866111981</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.6556021384723049</v>
+        <v>-1.216461706045896</v>
       </c>
       <c r="C116">
-        <v>-0.04186513289537194</v>
+        <v>0.004551860891105541</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.608245815741718</v>
+        <v>-0.7739463291748494</v>
       </c>
       <c r="C117">
-        <v>0.5616719954837028</v>
+        <v>-0.7663630574198417</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.6913977912240632</v>
+        <v>-0.913973801157048</v>
       </c>
       <c r="C118">
-        <v>-1.081755461434597</v>
+        <v>-1.448583447738505</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.5388937274487628</v>
+        <v>0.2344398681555251</v>
       </c>
       <c r="C119">
-        <v>2.159959715967747</v>
+        <v>-1.653262554243752</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.1848904679404867</v>
+        <v>0.8102463355103302</v>
       </c>
       <c r="C120">
-        <v>0.1529358343701809</v>
+        <v>0.3431823142310053</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>1.152763317407856</v>
+        <v>0.09803661372731674</v>
       </c>
       <c r="C121">
-        <v>-0.2547363574369722</v>
+        <v>0.3451500441046536</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-1.533235547434909</v>
+        <v>-0.8821970491580545</v>
       </c>
       <c r="C122">
-        <v>1.934624115036045</v>
+        <v>-1.606203768729986</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.4761200167171829</v>
+        <v>-0.4541990341634426</v>
       </c>
       <c r="C123">
-        <v>-0.3181669903953787</v>
+        <v>-0.7513967669074966</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>-1.053072300518098</v>
+        <v>0.3001869050261686</v>
       </c>
       <c r="C124">
-        <v>1.807693812323437</v>
+        <v>1.017721496463726</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>-0.2052118805841135</v>
+        <v>-0.01340680361322225</v>
       </c>
       <c r="C125">
-        <v>0.2582213985094421</v>
+        <v>0.4349227451480348</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.8463485899382269</v>
+        <v>0.7704965562442483</v>
       </c>
       <c r="C126">
-        <v>0.3705896280646346</v>
+        <v>1.49151681945928</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>-0.09029161479498675</v>
+        <v>-1.397795753077284</v>
       </c>
       <c r="C127">
-        <v>0.2586383029915243</v>
+        <v>-0.5529065478908179</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.977529091407011</v>
+        <v>-0.329788158650842</v>
       </c>
       <c r="C128">
-        <v>-0.1184483501630011</v>
+        <v>-0.4727234812557409</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.2948686196288613</v>
+        <v>-0.1842761802740215</v>
       </c>
       <c r="C129">
-        <v>-0.2925458161442557</v>
+        <v>0.3358705461781747</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.5125293619232754</v>
+        <v>-0.7048685982207639</v>
       </c>
       <c r="C130">
-        <v>-0.2519807089798019</v>
+        <v>-1.091970644314248</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9515166704301949</v>
+        <v>-1.090574579817913</v>
       </c>
       <c r="C131">
-        <v>-2.1993563358952</v>
+        <v>-0.06141376046699792</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>-0.09750259637545168</v>
+        <v>0.03618017714962641</v>
       </c>
       <c r="C132">
-        <v>1.032525233123633</v>
+        <v>0.496915657736265</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-1.389450453119165</v>
+        <v>-2.091757609818467</v>
       </c>
       <c r="C133">
-        <v>0.5512445753631879</v>
+        <v>0.557854193690363</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>-1.328540883663591</v>
+        <v>1.168650815174037</v>
       </c>
       <c r="C134">
-        <v>1.169004062583691</v>
+        <v>0.353692674102067</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>-0.3376472123555094</v>
+        <v>0.04363120761017542</v>
       </c>
       <c r="C135">
-        <v>0.8429518410697068</v>
+        <v>-0.8894642814084571</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>1.23772692152904</v>
+        <v>0.926859968116558</v>
       </c>
       <c r="C136">
-        <v>-0.4480510334701866</v>
+        <v>-0.9999976613802539</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.9679373021433593</v>
+        <v>-0.4501710873122424</v>
       </c>
       <c r="C137">
-        <v>-1.008968783179425</v>
+        <v>-0.005547793387422173</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>-0.2091400987183038</v>
+        <v>-0.03830468301868587</v>
       </c>
       <c r="C138">
-        <v>0.5251966596460658</v>
+        <v>-0.2914967042522241</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>-1.113696656687486</v>
+        <v>-1.088277776948597</v>
       </c>
       <c r="C139">
-        <v>0.4627862272752178</v>
+        <v>-1.521324718633585</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>-0.2978971516766892</v>
+        <v>-1.096126012710735</v>
       </c>
       <c r="C140">
-        <v>0.9448574118383355</v>
+        <v>0.03635383319965163</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.4236020940932985</v>
+        <v>-1.743895932475992</v>
       </c>
       <c r="C141">
-        <v>1.442194291688004</v>
+        <v>-1.381832886554923</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.117745256544975</v>
+        <v>-0.9524669681226062</v>
       </c>
       <c r="C142">
-        <v>0.5424243288364935</v>
+        <v>-0.4703468404224527</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>-1.092114927669431</v>
+        <v>-1.264245228894373</v>
       </c>
       <c r="C143">
-        <v>-1.062848470188597</v>
+        <v>0.07926482557771353</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>-0.2767698201147564</v>
+        <v>-0.4814763508222564</v>
       </c>
       <c r="C144">
-        <v>-0.4743555856464962</v>
+        <v>-0.4042888836028412</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>-1.106702838422568</v>
+        <v>0.2627913814932055</v>
       </c>
       <c r="C145">
-        <v>0.130262585135159</v>
+        <v>-0.3872858947631918</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-0.6935315895110786</v>
+        <v>-2.497553756117598</v>
       </c>
       <c r="C146">
-        <v>0.03576557742754552</v>
+        <v>-1.237353780706701</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.1601167398165971</v>
+        <v>-0.1758469823654004</v>
       </c>
       <c r="C147">
-        <v>0.5449053163273199</v>
+        <v>-0.2852668113888501</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>-0.2417910601131731</v>
+        <v>0.4323623824979151</v>
       </c>
       <c r="C148">
-        <v>-0.4023827624235848</v>
+        <v>1.220500977524624</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-1.480049385418802</v>
+        <v>-3.261014191686221</v>
       </c>
       <c r="C149">
-        <v>1.569484523180908</v>
+        <v>-1.607201243876677</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-2.336258179267366</v>
+        <v>0.760244037312804</v>
       </c>
       <c r="C150">
-        <v>0.5305886374064407</v>
+        <v>0.2799006163250939</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.385967548013626</v>
+        <v>-1.109611178412523</v>
       </c>
       <c r="C151">
-        <v>-0.4232773207646311</v>
+        <v>0.2771409789863233</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-0.4163459330920902</v>
+        <v>-0.9200414857716935</v>
       </c>
       <c r="C152">
-        <v>-0.06195348390507666</v>
+        <v>-1.330262003691687</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-1.310135019375638</v>
+        <v>0.7350929747749551</v>
       </c>
       <c r="C153">
-        <v>0.3025261210449234</v>
+        <v>0.8871434587186899</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>-0.3557756128180428</v>
+        <v>0.8117737231693486</v>
       </c>
       <c r="C154">
-        <v>3.021372735109653</v>
+        <v>1.386951564414399</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-0.2599554349510335</v>
+        <v>-1.443421647127494</v>
       </c>
       <c r="C155">
-        <v>0.06356773497980366</v>
+        <v>0.7629901650251429</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>-1.232240641331266</v>
+        <v>0.8314455293749966</v>
       </c>
       <c r="C156">
-        <v>-0.344600559338932</v>
+        <v>-2.02216829601272</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>-1.723815134680461</v>
+        <v>-1.458474411960839</v>
       </c>
       <c r="C157">
-        <v>1.514845504627876</v>
+        <v>-1.621944399219059</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-1.214432831323744</v>
+        <v>0.5156099782814183</v>
       </c>
       <c r="C158">
-        <v>0.4558307638178826</v>
+        <v>0.9279614896150495</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>0.1281161734626288</v>
+        <v>0.05917279145307335</v>
       </c>
       <c r="C159">
-        <v>-0.2711967748745623</v>
+        <v>0.03805367671765454</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.9916662341052022</v>
+        <v>-0.2248033505643226</v>
       </c>
       <c r="C160">
-        <v>-0.5772667137517324</v>
+        <v>0.04727752504328914</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>-0.886576715553023</v>
+        <v>0.09658831858103512</v>
       </c>
       <c r="C161">
-        <v>1.053823844015903</v>
+        <v>-0.2277871483717563</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>0.8714568372572897</v>
+        <v>0.1196530345962324</v>
       </c>
       <c r="C162">
-        <v>-2.362684405409751</v>
+        <v>-0.9646078281199181</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>0.5655631299343032</v>
+        <v>0.1150249188727445</v>
       </c>
       <c r="C163">
-        <v>1.479207863433359</v>
+        <v>-0.01787978190158057</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>1.171890597218861</v>
+        <v>-1.972761043548674</v>
       </c>
       <c r="C164">
-        <v>-1.535292063751015</v>
+        <v>-0.02695138434395228</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.3433887717393156</v>
+        <v>-1.411691221422446</v>
       </c>
       <c r="C165">
-        <v>0.8962297340604114</v>
+        <v>0.02859970072763141</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.06975464033381437</v>
+        <v>0.04329700266847518</v>
       </c>
       <c r="C166">
-        <v>-1.211581398207577</v>
+        <v>-1.143618839127823</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>0.5513618277385375</v>
+        <v>0.3506208283310556</v>
       </c>
       <c r="C167">
-        <v>0.9366007294208325</v>
+        <v>2.262726669968715</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>2.094120519502778</v>
+        <v>-1.908032330651552</v>
       </c>
       <c r="C168">
-        <v>-0.1021612176619354</v>
+        <v>-1.089052813847199</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>0.435431236340031</v>
+        <v>-0.6648422524894093</v>
       </c>
       <c r="C169">
-        <v>-0.1745571152814066</v>
+        <v>-0.6933914608575351</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.133581203016941</v>
+        <v>-0.2794770978584816</v>
       </c>
       <c r="C170">
-        <v>0.275757187267875</v>
+        <v>-0.005390435705692795</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>-1.728335366107873</v>
+        <v>-0.6493578152647917</v>
       </c>
       <c r="C171">
-        <v>0.895410157606219</v>
+        <v>-0.2347890497263645</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>-1.640214011065798</v>
+        <v>-0.2510470926613928</v>
       </c>
       <c r="C172">
-        <v>0.7736034568928956</v>
+        <v>1.267117380954277</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>-0.03187753596944357</v>
+        <v>1.004801355787241</v>
       </c>
       <c r="C173">
-        <v>0.5804148295939066</v>
+        <v>-1.723555870743209</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>-2.356185572733037</v>
+        <v>-2.023881775439552</v>
       </c>
       <c r="C174">
-        <v>-1.130564441132364</v>
+        <v>-1.966417263523969</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-0.5508959444895034</v>
+        <v>-2.953024066140234</v>
       </c>
       <c r="C175">
-        <v>1.237529147534164</v>
+        <v>-1.704137081982635</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>-1.296321992352482</v>
+        <v>-0.2206623247754693</v>
       </c>
       <c r="C176">
-        <v>1.765446166581306</v>
+        <v>1.316799295033895</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.08775406101041083</v>
+        <v>-0.9374201619788918</v>
       </c>
       <c r="C177">
-        <v>-1.105439854554691</v>
+        <v>-1.258271875212745</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-1.117719973972074</v>
+        <v>0.5111382425514974</v>
       </c>
       <c r="C178">
-        <v>-1.730382836097458</v>
+        <v>-0.4446432876259574</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-1.582298585401615</v>
+        <v>0.78490929417783</v>
       </c>
       <c r="C179">
-        <v>0.5192025940388399</v>
+        <v>0.9383008177029575</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>0.5586862703644778</v>
+        <v>-0.8016691391508622</v>
       </c>
       <c r="C180">
-        <v>-0.4968828495754068</v>
+        <v>0.4066666614520725</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>2.703026301668946</v>
+        <v>-0.902901801819962</v>
       </c>
       <c r="C181">
-        <v>0.09277642399259567</v>
+        <v>-0.4076680237537387</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>-0.6479221878100047</v>
+        <v>1.248427798714119</v>
       </c>
       <c r="C182">
-        <v>0.3373161685676878</v>
+        <v>0.4069156329689431</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>-0.5477325171595242</v>
+        <v>0.9489562566382679</v>
       </c>
       <c r="C183">
-        <v>1.452813936049023</v>
+        <v>0.1373085193531946</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>0.7633285178169915</v>
+        <v>0.3345993032079519</v>
       </c>
       <c r="C184">
-        <v>-0.109525869636056</v>
+        <v>0.04206654974795074</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>1.647330134964915</v>
+        <v>0.5781639997394497</v>
       </c>
       <c r="C185">
-        <v>-0.2058946253690299</v>
+        <v>-0.007502207193791188</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>0.1752268063994138</v>
+        <v>-0.7747469857109206</v>
       </c>
       <c r="C186">
-        <v>-0.8352693003792797</v>
+        <v>-0.407653029784097</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.6582537639339142</v>
+        <v>0.2038217244321805</v>
       </c>
       <c r="C187">
-        <v>-1.4796815313227</v>
+        <v>1.032007344174052</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>0.09227214625957399</v>
+        <v>-1.699811159280825</v>
       </c>
       <c r="C188">
-        <v>-0.9227119859364677</v>
+        <v>1.447937746304557</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-1.363267757198538</v>
+        <v>0.7282962935718276</v>
       </c>
       <c r="C189">
-        <v>0.2435260706491285</v>
+        <v>0.02582667218529178</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>0.9079850594221636</v>
+        <v>0.4618623767527623</v>
       </c>
       <c r="C190">
-        <v>0.06553601719205687</v>
+        <v>0.6147168321149981</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>0.7386272270055387</v>
+        <v>0.7207009230753706</v>
       </c>
       <c r="C191">
-        <v>0.2206307063451693</v>
+        <v>-1.053615484404483</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-0.3260440247600873</v>
+        <v>-0.5891872826323727</v>
       </c>
       <c r="C192">
-        <v>1.302324210687377</v>
+        <v>1.736505494105269</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-0.7123031636717292</v>
+        <v>0.4468148486835682</v>
       </c>
       <c r="C193">
-        <v>-1.657905572900111</v>
+        <v>0.2742518832246513</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>-0.7497177857950744</v>
+        <v>1.167061822194015</v>
       </c>
       <c r="C194">
-        <v>-0.6387374212905044</v>
+        <v>0.8590180639023723</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.8763302869564681</v>
+        <v>1.346666581808654</v>
       </c>
       <c r="C195">
-        <v>-1.006334873583484</v>
+        <v>0.3769246225439807</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>-2.009561975634771</v>
+        <v>-1.283826051585863</v>
       </c>
       <c r="C196">
-        <v>0.168223173307779</v>
+        <v>-1.381908461978742</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>0.9589954395382</v>
+        <v>1.126568967911118</v>
       </c>
       <c r="C197">
-        <v>0.556141099628869</v>
+        <v>0.8873822861881483</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.317520830205851</v>
+        <v>-1.124769575469718</v>
       </c>
       <c r="C198">
-        <v>-1.334015352709131</v>
+        <v>-0.07961431467696944</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>0.3890334935341447</v>
+        <v>0.6113956476500829</v>
       </c>
       <c r="C199">
-        <v>-0.4699629382573383</v>
+        <v>0.4803396096245971</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>0.05711085963957493</v>
+        <v>-1.381265536739976</v>
       </c>
       <c r="C200">
-        <v>0.1594939372445116</v>
+        <v>-1.313730370664287</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>0.3889569148504548</v>
+        <v>0.2416624037232297</v>
       </c>
       <c r="C201">
-        <v>-1.604705960691271</v>
+        <v>-0.5720319569336767</v>
       </c>
     </row>
   </sheetData>
